--- a/ExportExcel/Account Information Tests.xlsx
+++ b/ExportExcel/Account Information Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
   <si>
     <t>STT</t>
   </si>
@@ -38,97 +38,37 @@
     <t/>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>1755 ms</t>
-  </si>
-  <si>
-    <t>Họ tên không được cập nhật! expected [Nguyễn Văn A] but found [Innologic]</t>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>0 ms</t>
   </si>
   <si>
     <t>testEditBirthday</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>1421 ms</t>
-  </si>
-  <si>
     <t>testEditPhoneNumber</t>
   </si>
   <si>
-    <t>10124 ms</t>
-  </si>
-  <si>
-    <t>Expected condition failed: waiting for element to be clickable: By.xpath: //input[@placeholder='Số điện thoại'] (tried for 10 second(s) with 500 milliseconds interval)
-Build info: version: '4.28.1', revision: '73f5ad48a2'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64673}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64673/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: ea081ad99841f4cb0ad1345c47edb280</t>
-  </si>
-  <si>
     <t>testEditEmail</t>
   </si>
   <si>
-    <t>10133 ms</t>
-  </si>
-  <si>
-    <t>Expected condition failed: waiting for element to be clickable: By.xpath: //input[@id='fEmail'] (tried for 10 second(s) with 500 milliseconds interval)
-Build info: version: '4.28.1', revision: '73f5ad48a2'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64673}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64673/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: ea081ad99841f4cb0ad1345c47edb280</t>
-  </si>
-  <si>
     <t>testSelectMaleRadio</t>
   </si>
   <si>
-    <t>2590 ms</t>
-  </si>
-  <si>
     <t>testSelectFemaleRadio</t>
   </si>
   <si>
-    <t>2642 ms</t>
-  </si>
-  <si>
     <t>testUpdateAddress</t>
   </si>
   <si>
-    <t>16603 ms</t>
-  </si>
-  <si>
-    <t>no such element: Unable to locate element: {"method":"css selector","selector":"#address"}
-  (Session info: chrome=134.0.6998.178)
-For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Build info: version: '4.28.1', revision: '73f5ad48a2'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [ea081ad99841f4cb0ad1345c47edb280, findElement {using=id, value=address}]
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64673}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64673/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: ea081ad99841f4cb0ad1345c47edb280</t>
-  </si>
-  <si>
     <t>testSelectProvince</t>
   </si>
   <si>
-    <t>50082 ms</t>
-  </si>
-  <si>
     <t>testSelectDistrict</t>
   </si>
   <si>
-    <t>2774 ms</t>
-  </si>
-  <si>
     <t>testSelectWardAndSubmit</t>
-  </si>
-  <si>
-    <t>2896 ms</t>
   </si>
 </sst>
 </file>
@@ -201,9 +141,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="22.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -236,14 +176,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -251,16 +191,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="1">
-        <v>12</v>
+      <c r="D3" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -271,19 +211,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="2">
+      <c r="D4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -291,19 +231,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="2">
+      <c r="D5" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -311,16 +251,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="1">
-        <v>12</v>
+      <c r="D6" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -331,16 +271,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="1">
-        <v>12</v>
+      <c r="D7" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -351,19 +291,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="D8" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -371,16 +311,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="1">
-        <v>12</v>
+      <c r="D9" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -391,16 +331,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="1">
-        <v>12</v>
+      <c r="D10" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -411,16 +351,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="1">
-        <v>12</v>
+      <c r="D11" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>

--- a/ExportExcel/Account Information Tests.xlsx
+++ b/ExportExcel/Account Information Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>STT</t>
   </si>
@@ -38,37 +38,81 @@
     <t/>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>2396 ms</t>
+  </si>
+  <si>
+    <t>Họ tên không được cập nhật! expected [Nguyễn Văn A] but found [Innologic]</t>
   </si>
   <si>
     <t>testEditBirthday</t>
   </si>
   <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>2918 ms</t>
+  </si>
+  <si>
     <t>testEditPhoneNumber</t>
   </si>
   <si>
+    <t>4512 ms</t>
+  </si>
+  <si>
+    <t>Số điện thoại không nên khớp với giá trị từ Excel vì nó bị disabled! did not expect [0987770202] but found [0987770202]</t>
+  </si>
+  <si>
     <t>testEditEmail</t>
   </si>
   <si>
+    <t>11331 ms</t>
+  </si>
+  <si>
+    <t>Expected condition failed: waiting for element to be clickable: By.id: fEmail (tried for 10 second(s) with 500 milliseconds interval)
+Build info: version: '4.28.1', revision: '73f5ad48a2'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61155}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61155/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: f63467ebfed5a175c5622abbc6940d57</t>
+  </si>
+  <si>
     <t>testSelectMaleRadio</t>
   </si>
   <si>
+    <t>4966 ms</t>
+  </si>
+  <si>
     <t>testSelectFemaleRadio</t>
   </si>
   <si>
+    <t>4740 ms</t>
+  </si>
+  <si>
     <t>testUpdateAddress</t>
   </si>
   <si>
+    <t>4961 ms</t>
+  </si>
+  <si>
     <t>testSelectProvince</t>
   </si>
   <si>
+    <t>5119 ms</t>
+  </si>
+  <si>
     <t>testSelectDistrict</t>
   </si>
   <si>
+    <t>4580 ms</t>
+  </si>
+  <si>
     <t>testSelectWardAndSubmit</t>
+  </si>
+  <si>
+    <t>4775 ms</t>
   </si>
 </sst>
 </file>
@@ -141,9 +185,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="22.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -176,14 +220,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s" s="2">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -191,16 +235,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>8</v>
+      <c r="D3" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -211,19 +255,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s" s="2">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -231,19 +275,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s" s="2">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -251,16 +295,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>8</v>
+      <c r="D6" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -271,16 +315,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="0">
-        <v>8</v>
+      <c r="D7" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -291,16 +335,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="0">
-        <v>8</v>
+      <c r="D8" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>7</v>
@@ -311,16 +355,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>8</v>
+      <c r="D9" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -331,16 +375,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="0">
-        <v>8</v>
+      <c r="D10" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -351,16 +395,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="0">
-        <v>8</v>
+      <c r="D11" t="s" s="1">
+        <v>12</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>
